--- a/votos_linea.xlsx
+++ b/votos_linea.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Nombre</t>
   </si>
@@ -36,7 +36,64 @@
     <t>jose.botzoc.22@gmail.com</t>
   </si>
   <si>
+    <t>Ivan Alexander Ico Cuc</t>
+  </si>
+  <si>
+    <t>ivan.ico@cobanesmicoope.com</t>
+  </si>
+  <si>
+    <t>Ivan Alexander Ico Cu</t>
+  </si>
+  <si>
+    <t>ivanii5862@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria de los Angeles Aguilar Santiago</t>
+  </si>
+  <si>
+    <t>maria.aguilar@cobanesmicoope.com</t>
+  </si>
+  <si>
+    <t>jose raul botzo merida</t>
+  </si>
+  <si>
+    <t>jbotzocm@miumg.edu.gt</t>
+  </si>
+  <si>
     <t>jose.botzoc@cobanesmicoope.com</t>
+  </si>
+  <si>
+    <t>suspiro</t>
+  </si>
+  <si>
+    <t>suspirofinca@gmail.com</t>
+  </si>
+  <si>
+    <t>jagan</t>
+  </si>
+  <si>
+    <t>ijaganx@miumg.edu.gt</t>
+  </si>
+  <si>
+    <t>camposhermoza@gmail.com</t>
+  </si>
+  <si>
+    <t>aguilarmarieloscds@gmail.com</t>
+  </si>
+  <si>
+    <t>marag41639@gmail.com</t>
+  </si>
+  <si>
+    <t>maraguilar4949@gmail.com</t>
+  </si>
+  <si>
+    <t>3245655341601@ingenieria.usac.edu.gt</t>
+  </si>
+  <si>
+    <t>MAria de los Angeles Aguilar Santiago</t>
+  </si>
+  <si>
+    <t>maria.aguilar.santiago.01@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -339,26 +396,116 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1"/>
-    <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4">
+        <v>4.9352697E7</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4.5874587E7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
